--- a/DataExtracted/Critical appraisal data extraction form (Responses) March 12.xlsx
+++ b/DataExtracted/Critical appraisal data extraction form (Responses) March 12.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1513" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="171">
   <si>
     <t>Timestamp</t>
   </si>
@@ -512,6 +512,18 @@
   </si>
   <si>
     <t>10.5327/Z2176-94782514</t>
+  </si>
+  <si>
+    <t>Shivaprakash_2022</t>
+  </si>
+  <si>
+    <t>10.3390/su14127154</t>
+  </si>
+  <si>
+    <t>Campbell_2025</t>
+  </si>
+  <si>
+    <t>10.1139/er-2025-0136</t>
   </si>
 </sst>
 </file>
@@ -521,7 +533,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -533,22 +545,78 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F9FA"/>
+        <bgColor rgb="FFF8F9FA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF442F65"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFF8F9FA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF442F65"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFF8F9FA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF442F65"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -563,6 +631,32 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="3" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -643,7 +737,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:V72" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:V73" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="22">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="Extractor initials" id="2"/>
@@ -877,7 +971,7 @@
     <col customWidth="1" min="3" max="3" width="37.63"/>
     <col customWidth="1" min="4" max="4" width="18.88"/>
     <col customWidth="1" min="5" max="13" width="37.63"/>
-    <col customWidth="1" min="14" max="28" width="18.88"/>
+    <col customWidth="1" min="14" max="49" width="18.88"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
@@ -5574,16 +5668,16 @@
     </row>
     <row r="70" ht="22.5" customHeight="1">
       <c r="A70" s="3">
-        <v>46069.90752475694</v>
+        <v>46075.850753611114</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>105</v>
+        <v>163</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>106</v>
+        <v>164</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>25</v>
@@ -5598,10 +5692,10 @@
         <v>25</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K70" s="4" t="s">
         <v>25</v>
@@ -5616,7 +5710,7 @@
         <v>25</v>
       </c>
       <c r="O70" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P70" s="4" t="s">
         <v>25</v>
@@ -5628,7 +5722,7 @@
         <v>25</v>
       </c>
       <c r="S70" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T70" s="4" t="s">
         <v>25</v>
@@ -5642,22 +5736,22 @@
     </row>
     <row r="71" ht="22.5" customHeight="1">
       <c r="A71" s="3">
-        <v>46075.850753611114</v>
+        <v>46075.86457751157</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>25</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G71" s="4" t="s">
         <v>25</v>
@@ -5678,7 +5772,7 @@
         <v>25</v>
       </c>
       <c r="M71" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N71" s="4" t="s">
         <v>25</v>
@@ -5696,10 +5790,10 @@
         <v>25</v>
       </c>
       <c r="S71" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T71" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U71" s="4" t="s">
         <v>25</v>
@@ -5709,72 +5803,167 @@
       </c>
     </row>
     <row r="72" ht="22.5" customHeight="1">
-      <c r="A72" s="3">
-        <v>46075.86457751157</v>
-      </c>
-      <c r="B72" s="4" t="s">
+      <c r="A72" s="5">
+        <v>46069.91459490741</v>
+      </c>
+      <c r="B72" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F72" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K72" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L72" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="M72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O72" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="P72" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q72" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R72" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="S72" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="T72" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="U72" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="V72" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73" ht="22.5" customHeight="1">
+      <c r="A73" s="7">
+        <v>46100.78635296296</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H73" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I73" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="G72" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H72" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I72" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J72" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K72" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L72" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="M72" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="N72" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="O72" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="P72" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q72" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="R72" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="S72" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="T72" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="U72" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="V72" s="4" t="s">
-        <v>25</v>
-      </c>
+      <c r="J73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K73" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L73" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M73" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N73" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O73" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="P73" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q73" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="R73" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="S73" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="T73" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="U73" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="V73" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="W73" s="11"/>
+      <c r="X73" s="12"/>
+      <c r="Y73" s="12"/>
+      <c r="Z73" s="11"/>
+      <c r="AA73" s="11"/>
+      <c r="AB73" s="12"/>
+      <c r="AC73" s="12"/>
+      <c r="AD73" s="11"/>
+      <c r="AE73" s="12"/>
+      <c r="AF73" s="11"/>
+      <c r="AG73" s="11"/>
+      <c r="AH73" s="12"/>
+      <c r="AI73" s="11"/>
+      <c r="AJ73" s="12"/>
+      <c r="AK73" s="11"/>
+      <c r="AL73" s="11"/>
+      <c r="AM73" s="11"/>
+      <c r="AN73" s="12"/>
+      <c r="AO73" s="11"/>
+      <c r="AP73" s="12"/>
+      <c r="AQ73" s="13"/>
+      <c r="AR73" s="14"/>
+      <c r="AS73" s="14"/>
+      <c r="AT73" s="14"/>
+      <c r="AU73" s="14"/>
+      <c r="AV73" s="14"/>
+      <c r="AW73" s="14"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
